--- a/site/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/headings.xlsx
+++ b/site/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,6 +438,490 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>h_01JZW9E9B6ZZRTWQSYHXT2DAAF</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01JZW9E9B6ZZRTWQSYHXT2DAAF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Key Functions</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>h_01KG4G8M52X0H1382BKQAJQG71</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01KG4G8M52X0H1382BKQAJQG71</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Prerequisites</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>h_01JZW70JA70W2SCAXXM5NFYAK0</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01JZW70JA70W2SCAXXM5NFYAK0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Integration Setup</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>h_01F6EH0W486EMXD6A000X2Z4YZ</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01F6EH0W486EMXD6A000X2Z4YZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Create Integration</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01HXY3TX2QHXF1YJK3GCQQ87P7</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Configuration</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01JPQ8ZTEY7NJC2SRMDWPK964A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Applications</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01JPQ91FKVZHN9SQJEN1N0S3XQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01JPS6V3Y0HBETQWCMNHNHZAVN</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Integration Features</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>01K4A9SYGXKD4PRK6W9STNDTN3</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#01K4A9SYGXKD4PRK6W9STNDTN3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>General Settings</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>h_01JZT4V8HJ90QZAEZ9Z3TXBCDK</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01JZT4V8HJ90QZAEZ9Z3TXBCDK</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Worker Management</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>h_01KGMG4JM3JXCF60W9N6GEFS2V</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01KGMG4JM3JXCF60W9N6GEFS2V</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Manage Contact Lifecycle Management</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>h_01KGMG4JM39E5ES9AGZFATM7WD</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01KGMG4JM39E5ES9AGZFATM7WD</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Correlation Settings</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>h_01KGM450J1YK3FN478G7X08MGN</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01KGM450J1YK3FN478G7X08MGN</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Reporting</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Log Insights</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Debug Mode</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Attribute Mapper</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>h_01KGS7GWR0HGV51CVV377A1WX4</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01KGS7GWR0HGV51CVV377A1WX4</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/headings.xlsx
+++ b/site/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Manage Contact Lifecycle Management</t>
+          <t>SolarWinds Service Desk Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -705,7 +705,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Correlation Settings</t>
+          <t>ADP Workforce Now Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -727,7 +727,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Logging</t>
+          <t>Sensitive Data Management</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,19 +737,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>h_01KMCZVEC5SGQCEV0GMJFA2PPY</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01KMCZVEC5SGQCEV0GMJFA2PPY</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Reporting</t>
+          <t>Logging</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,19 +759,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01K04B51EEX43EAV95YABBP3F5</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Reporting</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,19 +781,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#01KG21C7RQCRB9NJP5ZN6VEHXX</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01K04H64FAB90EMWBN6K7GPF4W</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Debug Mode</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,41 +825,41 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Attribute Mapper</t>
+          <t>Debug Mode</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KGS7GWR0HGV51CVV377A1WX4</t>
+          <t>h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01KGS7GWR0HGV51CVV377A1WX4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,54 +869,98 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KGS7GWR0HGV51CVV377A1WX4</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01KGS7GWR0HGV51CVV377A1WX4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/headings.xlsx
+++ b/site/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/headings.xlsx
@@ -737,12 +737,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KMCZVEC5SGQCEV0GMJFA2PPY</t>
+          <t>h_01KMD3Q7VFNT5G983FPYECWBRK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01KMCZVEC5SGQCEV0GMJFA2PPY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01KMD3Q7VFNT5G983FPYECWBRK</t>
         </is>
       </c>
     </row>

--- a/site/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/headings.xlsx
+++ b/site/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -737,12 +737,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KMD3Q7VFNT5G983FPYECWBRK</t>
+          <t>h_01KMD76AMYESKCDMYCF9MGFEEG</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01KMD3Q7VFNT5G983FPYECWBRK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01KMD76AMYESKCDMYCF9MGFEEG</t>
         </is>
       </c>
     </row>
@@ -815,152 +815,240 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01KMD5HX6RZDKPDAS75W3C2BAC</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Debug Mode</t>
+          <t>Worker Creation Notifications</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
+          <t>h_01KMD76AMYDB3W1H9V4WE5VGZ9</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01KMD76AMYDB3W1H9V4WE5VGZ9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Worker Creation Failure Notifications</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KGS7GWR0HGV51CVV377A1WX4</t>
+          <t>h_01KMD76AMYEGM8M00XY3JKQ42T</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01KGS7GWR0HGV51CVV377A1WX4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01KMD76AMYEGM8M00XY3JKQ42T</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Skipping execution Notifications</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>h_01KMD76AMYZ7ECQ19C8X23TJNR</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01KMD76AMYZ7ECQ19C8X23TJNR</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01K10JE0BE3NC9YPVFVTZJBJ7B</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Debug Mode</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01KJ53FCW9MVRD5Y58BMAJGH9X</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>h_01KGS7GWR0HGV51CVV377A1WX4</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01KGS7GWR0HGV51CVV377A1WX4</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01KGHMQNFNBCR5J9J93JC1KRMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/headings.xlsx
+++ b/site/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/headings.xlsx
@@ -737,12 +737,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KMD76AMYESKCDMYCF9MGFEEG</t>
+          <t>h_01KMDAT6XVJRK5M10ND73CVKMZ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01KMD76AMYESKCDMYCF9MGFEEG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01KMDAT6XVJRK5M10ND73CVKMZ</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KMD76AMYDB3W1H9V4WE5VGZ9</t>
+          <t>h_01KMDAT6XVW3YKX0X0WEZ63FFD</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01KMD76AMYDB3W1H9V4WE5VGZ9</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01KMDAT6XVW3YKX0X0WEZ63FFD</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KMD76AMYEGM8M00XY3JKQ42T</t>
+          <t>h_01KMDAT6XVX7P5XBK8G89VGAHN</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01KMD76AMYEGM8M00XY3JKQ42T</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01KMDAT6XVX7P5XBK8G89VGAHN</t>
         </is>
       </c>
     </row>
@@ -891,12 +891,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KMD76AMYZ7ECQ19C8X23TJNR</t>
+          <t>h_01KMDAT6XVAW55E3QGF1M64R2W</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01KMD76AMYZ7ECQ19C8X23TJNR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/SolarWinds-Service-Desk-ADP-Workforce-Now-Integration-Guide/#h_01KMDAT6XVAW55E3QGF1M64R2W</t>
         </is>
       </c>
     </row>
